--- a/tests/files/excel_module_test.xlsx
+++ b/tests/files/excel_module_test.xlsx
@@ -8,30 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agmontesb\Documents\GitHub\excel\tests\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9CE01CA-C860-4576-80B7-286F700B332B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0243AADF-E085-4F5B-A31D-FC84871972E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{CED12BA2-43D2-47A9-B18E-5C360477AC92}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{CED12BA2-43D2-47A9-B18E-5C360477AC92}"/>
   </bookViews>
   <sheets>
-    <sheet name="No links, No parameters" sheetId="1" r:id="rId1"/>
+    <sheet name="Outer links, outer parameter" sheetId="3" r:id="rId1"/>
     <sheet name="Parameters and inner links" sheetId="2" r:id="rId2"/>
-    <sheet name="Outer links, outer parameter" sheetId="3" r:id="rId3"/>
+    <sheet name="No links, No parameters" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -161,13 +150,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,151 +471,115 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C457F7C5-9D4D-42A1-8E4E-EC64623065D7}">
-  <dimension ref="F3:I15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30E2A6B8-B6B3-4D14-A216-B5187B5CE087}">
+  <dimension ref="E3:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F4" t="s">
+    <row r="3" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <f>+'No links, No parameters'!G4</f>
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <f>+'Parameters and inner links'!G4</f>
+        <v>250</v>
+      </c>
+      <c r="H3">
+        <f>+G3-F3</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4">
+        <f>+'No links, No parameters'!G5*'Parameters and inner links'!G2</f>
         <v>0</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <f>+'Parameters and inner links'!G5</f>
+        <v>230</v>
       </c>
       <c r="H4">
-        <v>55</v>
-      </c>
-      <c r="I4">
-        <f>+G4+H4</f>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F5" t="s">
-        <v>1</v>
+        <f t="shared" ref="H4:H7" si="0">+G4-F4</f>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <f>+'No links, No parameters'!G6</f>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>20</v>
+        <f>+'Parameters and inner links'!G6</f>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>75</v>
-      </c>
-      <c r="I5">
-        <f t="shared" ref="I5:I8" si="0">+G5+H5</f>
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F6" t="s">
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6">
+        <f>+'No links, No parameters'!G7</f>
+        <v>40</v>
       </c>
       <c r="G6">
-        <v>30</v>
+        <f>+'Parameters and inner links'!G7</f>
+        <v>85</v>
       </c>
       <c r="H6">
-        <v>95</v>
-      </c>
-      <c r="I6">
         <f t="shared" si="0"/>
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F7" t="s">
-        <v>3</v>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7">
+        <f>+'No links, No parameters'!G8</f>
+        <v>50</v>
       </c>
       <c r="G7">
-        <v>40</v>
+        <f>+'Parameters and inner links'!G8</f>
+        <v>18</v>
       </c>
       <c r="H7">
-        <v>115</v>
-      </c>
-      <c r="I7">
-        <f>+H7/G7</f>
-        <v>2.875</v>
-      </c>
-    </row>
-    <row r="8" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F8" t="s">
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>-32</v>
+      </c>
+    </row>
+    <row r="8" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="F8">
+        <f>+SUM(F3:F7)</f>
+        <v>130</v>
       </c>
       <c r="G8">
-        <v>50</v>
+        <f t="shared" ref="G8:H8" si="1">+SUM(G3:G7)</f>
+        <v>683</v>
       </c>
       <c r="H8">
-        <v>135</v>
-      </c>
-      <c r="I8">
-        <f t="shared" si="0"/>
-        <v>185</v>
-      </c>
-    </row>
-    <row r="9" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9">
-        <f>+SUM(G4:G8)</f>
-        <v>150</v>
-      </c>
-      <c r="H9">
-        <f t="shared" ref="H9:I9" si="1">+SUM(H4:H8)</f>
-        <v>475</v>
-      </c>
-      <c r="I9">
         <f t="shared" si="1"/>
-        <v>472.875</v>
-      </c>
-    </row>
-    <row r="12" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G13">
-        <v>300</v>
-      </c>
-      <c r="H13">
-        <f>20*G13</f>
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="14" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F14" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14">
-        <v>150</v>
-      </c>
-      <c r="H14">
-        <f>20*G14</f>
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="15" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15">
-        <f>+SUM(G13:G14)</f>
-        <v>450</v>
-      </c>
-      <c r="H15">
-        <f>+SUM(H13:H14)</f>
-        <v>9000</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="H8" evalError="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -826,114 +780,160 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30E2A6B8-B6B3-4D14-A216-B5187B5CE087}">
-  <dimension ref="E3:H8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C457F7C5-9D4D-42A1-8E4E-EC64623065D7}">
+  <dimension ref="F3:I15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="9" max="9" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E3" t="s">
+    <row r="3" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>10</v>
+      </c>
+      <c r="H4">
+        <v>55</v>
+      </c>
+      <c r="I4">
+        <f>+G4+H4</f>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>20</v>
+      </c>
+      <c r="H5">
+        <v>75</v>
+      </c>
+      <c r="I5">
+        <f t="shared" ref="I5:I8" si="0">+G5+H5</f>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>30</v>
+      </c>
+      <c r="H6">
+        <v>95</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>40</v>
+      </c>
+      <c r="H7">
+        <v>115</v>
+      </c>
+      <c r="I7">
+        <f>+H7/G7</f>
+        <v>2.875</v>
+      </c>
+    </row>
+    <row r="8" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F8" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8">
+        <v>50</v>
+      </c>
+      <c r="H8">
+        <v>135</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="9" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9">
+        <f>+SUM(G4:G8)</f>
+        <v>150</v>
+      </c>
+      <c r="H9">
+        <f t="shared" ref="H9:I9" si="1">+SUM(H4:H8)</f>
+        <v>475</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="1"/>
+        <v>472.875</v>
+      </c>
+    </row>
+    <row r="12" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F12" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" s="6">
+        <v>41237</v>
+      </c>
+    </row>
+    <row r="13" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F13" t="s">
         <v>8</v>
       </c>
-      <c r="F3">
-        <f>+'No links, No parameters'!G4</f>
+      <c r="G13">
+        <v>300</v>
+      </c>
+      <c r="H13">
+        <f>20*G13</f>
+        <v>6000</v>
+      </c>
+      <c r="I13" t="str">
+        <f>+F12&amp;F15</f>
+        <v>Tabla 2:toal</v>
+      </c>
+    </row>
+    <row r="14" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14">
+        <v>150</v>
+      </c>
+      <c r="H14">
+        <f>20*G14</f>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="15" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F15" t="s">
         <v>10</v>
       </c>
-      <c r="G3">
-        <f>+'Parameters and inner links'!G4</f>
-        <v>250</v>
-      </c>
-      <c r="H3">
-        <f>+G3-F3</f>
-        <v>240</v>
-      </c>
-    </row>
-    <row r="4" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4">
-        <f>+'No links, No parameters'!G5*'Parameters and inner links'!G2</f>
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <f>+'Parameters and inner links'!G5</f>
-        <v>230</v>
-      </c>
-      <c r="H4">
-        <f t="shared" ref="H4:H7" si="0">+G4-F4</f>
-        <v>230</v>
-      </c>
-    </row>
-    <row r="5" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5">
-        <f>+'No links, No parameters'!G6</f>
-        <v>30</v>
-      </c>
-      <c r="G5">
-        <f>+'Parameters and inner links'!G6</f>
-        <v>100</v>
-      </c>
-      <c r="H5">
-        <f t="shared" si="0"/>
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6">
-        <f>+'No links, No parameters'!G7</f>
-        <v>40</v>
-      </c>
-      <c r="G6">
-        <f>+'Parameters and inner links'!G7</f>
-        <v>85</v>
-      </c>
-      <c r="H6">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7">
-        <f>+'No links, No parameters'!G8</f>
-        <v>50</v>
-      </c>
-      <c r="G7">
-        <f>+'Parameters and inner links'!G8</f>
-        <v>18</v>
-      </c>
-      <c r="H7">
-        <f t="shared" si="0"/>
-        <v>-32</v>
-      </c>
-    </row>
-    <row r="8" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="F8">
-        <f>+SUM(F3:F7)</f>
-        <v>130</v>
-      </c>
-      <c r="G8">
-        <f t="shared" ref="G8:H8" si="1">+SUM(G3:G7)</f>
-        <v>683</v>
-      </c>
-      <c r="H8">
-        <f t="shared" si="1"/>
-        <v>553</v>
+      <c r="G15">
+        <f>+SUM(G13:G14)</f>
+        <v>450</v>
+      </c>
+      <c r="H15">
+        <f>+SUM(H13:H14)</f>
+        <v>9000</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="H8" evalError="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/tests/files/excel_module_test.xlsx
+++ b/tests/files/excel_module_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agmontesb\Documents\GitHub\excel\tests\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0243AADF-E085-4F5B-A31D-FC84871972E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FD918EC-7AAF-4EB9-A323-BF4A5D443EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{CED12BA2-43D2-47A9-B18E-5C360477AC92}"/>
   </bookViews>
@@ -17,6 +17,11 @@
     <sheet name="Parameters and inner links" sheetId="2" r:id="rId2"/>
     <sheet name="No links, No parameters" sheetId="1" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="nombres">'No links, No parameters'!$F$5:$F$9</definedName>
+    <definedName name="tabla1">'Parameters and inner links'!$E$12:$H$17</definedName>
+    <definedName name="tabla2">'Outer links, outer parameter'!$E$5:$H$7</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -585,7 +590,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBA4B623-7162-486F-AC03-D766E050D9E6}">
-  <dimension ref="E2:H17"/>
+  <dimension ref="E2:H21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="12.42578125" customWidth="1"/>
@@ -714,7 +719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="5:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="E14" t="s">
         <v>9</v>
       </c>
@@ -729,7 +734,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="5:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="E15" t="s">
         <v>12</v>
       </c>
@@ -744,7 +749,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="5:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
         <v>13</v>
       </c>
@@ -760,7 +765,7 @@
         <v>2518</v>
       </c>
     </row>
-    <row r="17" spans="6:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="6:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="F17">
         <f>+F16+F15+F14</f>
         <v>105</v>
@@ -774,6 +779,10 @@
         <v>2606</v>
       </c>
     </row>
+    <row r="18" spans="6:8" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="6:8" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="6:8" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="6:8" hidden="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -784,6 +793,7 @@
   <dimension ref="F3:I15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="7" max="8" width="0" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/tests/files/excel_module_test.xlsx
+++ b/tests/files/excel_module_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agmontesb\Documents\GitHub\excel\tests\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FD918EC-7AAF-4EB9-A323-BF4A5D443EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5937BBB5-1AB3-4599-8A97-D8B9FFEB67A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{CED12BA2-43D2-47A9-B18E-5C360477AC92}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{CED12BA2-43D2-47A9-B18E-5C360477AC92}"/>
   </bookViews>
   <sheets>
     <sheet name="Outer links, outer parameter" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="18">
   <si>
     <t>uno</t>
   </si>
@@ -83,13 +83,19 @@
   </si>
   <si>
     <t>tabla 2:</t>
+  </si>
+  <si>
+    <t>alex</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,6 +118,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -152,10 +165,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -163,8 +177,12 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="40" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -590,13 +608,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBA4B623-7162-486F-AC03-D766E050D9E6}">
-  <dimension ref="E2:H21"/>
+  <dimension ref="A2:H17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="5" width="9.140625" customWidth="1"/>
     <col min="6" max="6" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F2" t="s">
         <v>15</v>
       </c>
@@ -604,12 +623,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
@@ -624,7 +655,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="5" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E5" t="s">
         <v>9</v>
       </c>
@@ -639,7 +670,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="6" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E6" t="s">
         <v>12</v>
       </c>
@@ -654,7 +685,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="7" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E7" t="s">
         <v>13</v>
       </c>
@@ -669,7 +700,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="8" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E8" t="s">
         <v>14</v>
       </c>
@@ -684,7 +715,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F9">
         <f>+SUM(F4:F8)</f>
         <v>2413</v>
@@ -698,12 +729,12 @@
         <v>3096</v>
       </c>
     </row>
-    <row r="12" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E13" t="s">
         <v>8</v>
       </c>
@@ -719,7 +750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="5:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E14" t="s">
         <v>9</v>
       </c>
@@ -734,7 +765,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="5:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E15" t="s">
         <v>12</v>
       </c>
@@ -749,7 +780,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="5:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
         <v>13</v>
       </c>
@@ -765,7 +796,7 @@
         <v>2518</v>
       </c>
     </row>
-    <row r="17" spans="6:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="6:8" x14ac:dyDescent="0.25">
       <c r="F17">
         <f>+F16+F15+F14</f>
         <v>105</v>
@@ -779,10 +810,6 @@
         <v>2606</v>
       </c>
     </row>
-    <row r="18" spans="6:8" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="6:8" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="6:8" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="6:8" hidden="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -790,11 +817,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C457F7C5-9D4D-42A1-8E4E-EC64623065D7}">
-  <dimension ref="F3:I15"/>
+  <dimension ref="F3:M18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="8" width="0" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" customWidth="1"/>
+    <col min="9" max="9" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="6:9" x14ac:dyDescent="0.25">
@@ -913,10 +942,6 @@
         <f>20*G13</f>
         <v>6000</v>
       </c>
-      <c r="I13" t="str">
-        <f>+F12&amp;F15</f>
-        <v>Tabla 2:toal</v>
-      </c>
     </row>
     <row r="14" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F14" t="s">
@@ -941,6 +966,40 @@
       <c r="H15">
         <f>+SUM(H13:H14)</f>
         <v>9000</v>
+      </c>
+    </row>
+    <row r="17" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="F17" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="6">
+        <v>46016</v>
+      </c>
+      <c r="J17" t="e">
+        <f>3/0</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K17">
+        <v>253</v>
+      </c>
+      <c r="L17" t="s">
+        <v>17</v>
+      </c>
+      <c r="M17" t="str">
+        <f>+L17&amp;F15</f>
+        <v>alextoal</v>
+      </c>
+    </row>
+    <row r="18" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="F18" s="7">
+        <v>12345</v>
+      </c>
+      <c r="I18" s="9">
+        <v>46016</v>
+      </c>
+      <c r="J18" s="8">
+        <v>123456</v>
       </c>
     </row>
   </sheetData>

--- a/tests/files/excel_module_test.xlsx
+++ b/tests/files/excel_module_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agmontesb\Documents\GitHub\excel\tests\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5937BBB5-1AB3-4599-8A97-D8B9FFEB67A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD1C664E-E6FD-47F4-A1E9-49334D5F3395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{CED12BA2-43D2-47A9-B18E-5C360477AC92}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <definedName name="tabla1">'Parameters and inner links'!$E$12:$H$17</definedName>
     <definedName name="tabla2">'Outer links, outer parameter'!$E$5:$H$7</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcOnSave="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -92,8 +92,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -169,9 +170,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -180,6 +180,10 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="40" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -608,14 +612,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBA4B623-7162-486F-AC03-D766E050D9E6}">
-  <dimension ref="A2:H17"/>
+  <dimension ref="A2:I17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="9.140625" customWidth="1"/>
     <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" style="9" customWidth="1"/>
+    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F2" t="s">
         <v>15</v>
       </c>
@@ -623,7 +629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -634,7 +640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="39.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -650,12 +656,15 @@
       <c r="G4">
         <v>250</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4" s="10">
         <f>+G4+F4</f>
         <v>950</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4">
+        <v>123456789</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E5" t="s">
         <v>9</v>
       </c>
@@ -665,12 +674,12 @@
       <c r="G5">
         <v>230</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5" s="10">
         <f>+G5+F5</f>
         <v>1430</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="E6" t="s">
         <v>12</v>
       </c>
@@ -680,12 +689,12 @@
       <c r="G6">
         <v>100</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6" s="10">
         <f>+G6+F6</f>
         <v>440</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E7" t="s">
         <v>13</v>
       </c>
@@ -695,12 +704,12 @@
       <c r="G7">
         <v>85</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7" s="10">
         <f>+G7+F7</f>
         <v>213</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E8" t="s">
         <v>14</v>
       </c>
@@ -710,12 +719,12 @@
       <c r="G8">
         <v>18</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="10">
         <f>+G8+F8</f>
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F9">
         <f>+SUM(F4:F8)</f>
         <v>2413</v>
@@ -724,17 +733,17 @@
         <f>+SUM(G4:G8)</f>
         <v>683</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9" s="10">
         <f>+SUM(H4:H8)</f>
         <v>3096</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E13" t="s">
         <v>8</v>
       </c>
@@ -745,53 +754,53 @@
         <f>+G6</f>
         <v>100</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13" s="10">
         <f>+$G$2*F13</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14">
         <v>10</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="4">
         <v>25</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="11">
         <f>+SUM(F14:G14)</f>
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E15" t="s">
         <v>12</v>
       </c>
       <c r="F15">
         <v>15</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="4">
         <v>38</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="11">
         <f>+SUM(F15:G15)</f>
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="3">
         <v>80</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="2">
         <f>+F9 + F13</f>
         <v>2438</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="12">
         <f>+SUM(F16:G16)</f>
         <v>2518</v>
       </c>
@@ -801,11 +810,11 @@
         <f>+F16+F15+F14</f>
         <v>105</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="1">
         <f>+G16+G15+G14</f>
         <v>2501</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="12">
         <f>+H16+H15+H14</f>
         <v>2606</v>
       </c>
@@ -927,7 +936,7 @@
       <c r="F12" t="s">
         <v>7</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="5">
         <v>41237</v>
       </c>
     </row>
@@ -973,7 +982,7 @@
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="5">
         <v>46016</v>
       </c>
       <c r="J17" t="e">
@@ -992,13 +1001,13 @@
       </c>
     </row>
     <row r="18" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F18" s="7">
+      <c r="F18" s="6">
         <v>12345</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="8">
         <v>46016</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="7">
         <v>123456</v>
       </c>
     </row>

--- a/tests/files/excel_module_test.xlsx
+++ b/tests/files/excel_module_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agmontesb\Documents\GitHub\excel\tests\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD1C664E-E6FD-47F4-A1E9-49334D5F3395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7CEC61-3D59-4935-834A-6971AA5AA3E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{CED12BA2-43D2-47A9-B18E-5C360477AC92}"/>
   </bookViews>
